--- a/survey_templates/033_self_audit_likert_scale_survey--survey_templates.xlsx
+++ b/survey_templates/033_self_audit_likert_scale_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How often do you receive feedback from managers or supervisors?</t>
+          <t>Feedback Mechanisms</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How secure do you feel about your job security?</t>
+          <t>Job Security 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>How satisfied are you with leadership support?</t>
+          <t>Leadership Support 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>How satisfied are you with communication?</t>
+          <t>Communication 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>How do you rate your own performance?</t>
+          <t>Job Performance 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>How satisfied are you with leadership support?</t>
+          <t>Leadership Support 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How satisfied are you with work-life balance?</t>
+          <t>Work Life Balance 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_much'}</t>
+          <t>not_much</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not much'}</t>
+          <t>Not much</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_secure'}</t>
+          <t>very_secure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Secure'}</t>
+          <t>Very Secure</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_secure'}</t>
+          <t>somewhat_secure</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Secure'}</t>
+          <t>Somewhat Secure</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very_secure'}</t>
+          <t>not_very_secure</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not very secure'}</t>
+          <t>Not very secure</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all_secure'}</t>
+          <t>not_at_all_secure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all secure'}</t>
+          <t>Not at all secure</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_insecure'}</t>
+          <t>very_insecure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Insecure'}</t>
+          <t>Very Insecure</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Strongly Agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Agree'}</t>
+          <t>Somewhat Agree</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat Disagree'}</t>
+          <t>Somewhat Disagree</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Strongly Disagree'}</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sometime'}</t>
+          <t>sometime</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sometime'}</t>
+          <t>Sometime</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'almost_never'}</t>
+          <t>almost_never</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Almost Never'}</t>
+          <t>Almost Never</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Important'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not very important'}</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all_important'}</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all important'}</t>
+          <t>Not at all important</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>work_life_balance_2_choices</t>
+          <t>communication_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'not_at_all_important'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Not at all important'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'often'}</t>
+          <t>sometime</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Often'}</t>
+          <t>Sometime</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sometime'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sometime'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rarely'}</t>
+          <t>almost_never</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rarely'}</t>
+          <t>Almost Never</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'almost_never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Almost Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>communication_2_choices</t>
+          <t>work_environment_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'never'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Never'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Important'}</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
@@ -1675,46 +1675,46 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very_important'}</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not very important'}</t>
+          <t>Not at all important</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>work_environment_choices</t>
+          <t>job_involvement_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all_important'}</t>
+          <t>very_involved</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all important'}</t>
+          <t>Very Involved</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>work_environment_choices</t>
+          <t>job_involvement_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'not_at_all_important'}</t>
+          <t>somewhat_involved</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Not at all important'}</t>
+          <t>Somewhat Involved</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_involved'}</t>
+          <t>not_very_involved</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Involved'}</t>
+          <t>Not very Involved</t>
         </is>
       </c>
     </row>
@@ -1743,63 +1743,63 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_involved'}</t>
+          <t>not_at_all_involved</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Involved'}</t>
+          <t>Not at all Involved</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>job_involvement_choices</t>
+          <t>feedback_mechanisms_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very_involved'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not very Involved'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>job_involvement_choices</t>
+          <t>feedback_mechanisms_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all_involved'}</t>
+          <t>sometime</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all Involved'}</t>
+          <t>Sometime</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>job_involvement_choices</t>
+          <t>feedback_mechanisms_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'not_at_all_involved'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Not at all Involved'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'often'}</t>
+          <t>almost_never</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Often'}</t>
+          <t>Almost Never</t>
         </is>
       </c>
     </row>
@@ -1828,63 +1828,63 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sometime'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sometime'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>feedback_mechanisms_choices</t>
+          <t>job_performance_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rarely'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rarely'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>feedback_mechanisms_choices</t>
+          <t>job_performance_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'almost_never'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Almost Never'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>feedback_mechanisms_choices</t>
+          <t>job_performance_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'never'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Never'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1913,63 +1913,63 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>job_performance_choices</t>
+          <t>work_life_balance_3_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fair'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fair'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>job_performance_choices</t>
+          <t>work_life_balance_3_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'poor'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Poor'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>job_performance_choices</t>
+          <t>work_life_balance_3_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_poor'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Poor'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1998,63 +1998,63 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>work_life_balance_3_choices</t>
+          <t>leadership_support_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>work_life_balance_3_choices</t>
+          <t>leadership_support_2_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>work_life_balance_3_choices</t>
+          <t>leadership_support_2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Dissatisfied'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2083,63 +2083,63 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>leadership_support_2_choices</t>
+          <t>communication_3_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>leadership_support_2_choices</t>
+          <t>communication_3_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>leadership_support_2_choices</t>
+          <t>communication_3_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Dissatisfied'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2168,63 +2168,63 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>communication_3_choices</t>
+          <t>work_life_balance_4_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>communication_3_choices</t>
+          <t>work_life_balance_4_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>communication_3_choices</t>
+          <t>work_life_balance_4_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Dissatisfied'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2253,63 +2253,63 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>work_life_balance_4_choices</t>
+          <t>team_support_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>very_supportive</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Very Supportive</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>work_life_balance_4_choices</t>
+          <t>team_support_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_supportive</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Supportive</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>work_life_balance_4_choices</t>
+          <t>team_support_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Dissatisfied'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_supportive'}</t>
+          <t>somewhat_unsupportive</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Supportive'}</t>
+          <t>Somewhat Unsupportive</t>
         </is>
       </c>
     </row>
@@ -2338,63 +2338,63 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_supportive'}</t>
+          <t>very_unsupportive</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Supportive'}</t>
+          <t>Very Unsupportive</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>team_support_choices</t>
+          <t>opportunities_for_learning_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>team_support_choices</t>
+          <t>opportunities_for_learning_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_unsupportive'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat Unsupportive'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>team_support_choices</t>
+          <t>opportunities_for_learning_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_unsupportive'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Unsupportive'}</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
@@ -2406,80 +2406,80 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_important'}</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Important'}</t>
+          <t>Not at all important</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>opportunities_for_learning_choices</t>
+          <t>job_security_2_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_important'}</t>
+          <t>very_secure</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Important'}</t>
+          <t>Very Secure</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>opportunities_for_learning_choices</t>
+          <t>job_security_2_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very_important'}</t>
+          <t>somewhat_secure</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not very important'}</t>
+          <t>Somewhat Secure</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>opportunities_for_learning_choices</t>
+          <t>job_security_2_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all_important'}</t>
+          <t>not_very_secure</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all important'}</t>
+          <t>Not very secure</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>opportunities_for_learning_choices</t>
+          <t>job_security_2_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'not_at_all_important'}</t>
+          <t>not_at_all_secure</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Not at all important'}</t>
+          <t>Not at all secure</t>
         </is>
       </c>
     </row>
@@ -2491,80 +2491,80 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_secure'}</t>
+          <t>very_insecure</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Secure'}</t>
+          <t>Very Insecure</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>job_security_2_choices</t>
+          <t>leadership_support_3_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_secure'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Secure'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>job_security_2_choices</t>
+          <t>leadership_support_3_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very_secure'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not very secure'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>job_security_2_choices</t>
+          <t>leadership_support_3_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all_secure'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all secure'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>job_security_2_choices</t>
+          <t>leadership_support_3_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_insecure'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Insecure'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2576,80 +2576,80 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>leadership_support_3_choices</t>
+          <t>communication_4_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>leadership_support_3_choices</t>
+          <t>communication_4_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>leadership_support_3_choices</t>
+          <t>communication_4_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_dissatisfied'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>leadership_support_3_choices</t>
+          <t>communication_4_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2661,80 +2661,80 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>communication_4_choices</t>
+          <t>team_dynamics_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>communication_4_choices</t>
+          <t>team_dynamics_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>communication_4_choices</t>
+          <t>team_dynamics_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_dissatisfied'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>communication_4_choices</t>
+          <t>team_dynamics_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2746,80 +2746,80 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>team_dynamics_choices</t>
+          <t>job_performance_2_choices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>team_dynamics_choices</t>
+          <t>job_performance_2_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>team_dynamics_choices</t>
+          <t>job_performance_2_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_dissatisfied'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>team_dynamics_choices</t>
+          <t>job_performance_2_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Dissatisfied'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -2831,80 +2831,80 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>job_performance_2_choices</t>
+          <t>leadership_support_4_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>job_performance_2_choices</t>
+          <t>leadership_support_4_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'fair'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Fair'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>job_performance_2_choices</t>
+          <t>leadership_support_4_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'poor'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Poor'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>job_performance_2_choices</t>
+          <t>leadership_support_4_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_poor'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Poor'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2916,80 +2916,80 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>leadership_support_4_choices</t>
+          <t>work_life_balance_5_choices</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>leadership_support_4_choices</t>
+          <t>work_life_balance_5_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>leadership_support_4_choices</t>
+          <t>work_life_balance_5_choices</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_dissatisfied'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>leadership_support_4_choices</t>
+          <t>work_life_balance_5_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -3001,80 +3001,80 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>work_life_balance_5_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>work_life_balance_5_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>work_life_balance_5_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_dissatisfied'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>work_life_balance_5_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -3086,80 +3086,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>job_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>job_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>job_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'somewhat_dissatisfied'}</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'Somewhat Dissatisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>job_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
